--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3046,6 +3046,135 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113466219</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97314</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mantesåsen (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>562812</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6633264</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>U-Sur-0563</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>foto i AP</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>113466219</v>
       </c>
       <c r="B21" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>113466219</v>
       </c>
       <c r="B21" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>113466219</v>
       </c>
       <c r="B21" t="n">
-        <v>97348</v>
+        <v>97349</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>foto i AP</t>
+          <t>ett tiotal förekomster i norra åsslänten, foto i AP (OK)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3157,6 +3157,11 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>gammal åsbarrskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>113466219</v>
       </c>
       <c r="B21" t="n">
-        <v>97349</v>
+        <v>97352</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>113466219</v>
       </c>
       <c r="B21" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>113466219</v>
       </c>
       <c r="B21" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>113466219</v>
       </c>
       <c r="B21" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>113466219</v>
       </c>
       <c r="B21" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -3051,7 +3051,7 @@
         <v>113466219</v>
       </c>
       <c r="B21" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 69624-2018 artfynd.xlsx
+++ b/artfynd/A 69624-2018 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
